--- a/outputs/monitor_xlsx/20260413.xlsx
+++ b/outputs/monitor_xlsx/20260413.xlsx
@@ -544,10 +544,6 @@
           <t>+1.60%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+2.02%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-0.39%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+0.49%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.14%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+1.68%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-0.57%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-0.25%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-161.79億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>344.56億</t>
@@ -807,7 +769,6 @@
           <t>60.5億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>24.36億</t>
@@ -818,8 +779,6 @@
           <t>121.82億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>140.89%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>130.81%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-61.41億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>13325口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8613口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-77.95億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-51.54億</t>
@@ -1015,10 +960,6 @@
           <t>None億</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1175,6 +1116,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1295,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1303,26 +1245,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.19</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>91689</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>30857</v>
       </c>
       <c r="H4" t="n">
-        <v>197295</v>
+        <v>228153</v>
       </c>
       <c r="I4" t="n">
         <v>242</v>
       </c>
       <c r="J4" t="n">
-        <v>1474</v>
+        <v>1716</v>
       </c>
       <c r="K4" t="n">
         <v>10841</v>
@@ -1331,11 +1273,14 @@
         <v>9105</v>
       </c>
       <c r="M4" t="n">
-        <v>44171</v>
+        <v>53276</v>
       </c>
       <c r="N4" t="n">
         <v>-4616097</v>
       </c>
+      <c r="O4" t="n">
+        <v>5.76</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1358,26 +1303,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>817</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0.37</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>1446</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-165</v>
       </c>
       <c r="H5" t="n">
-        <v>-562</v>
+        <v>-727</v>
       </c>
       <c r="I5" t="n">
         <v>-7</v>
       </c>
       <c r="J5" t="n">
-        <v>-101</v>
+        <v>-108</v>
       </c>
       <c r="K5" t="n">
         <v>52</v>
@@ -1386,11 +1331,14 @@
         <v>2706</v>
       </c>
       <c r="M5" t="n">
-        <v>10707</v>
+        <v>13413</v>
       </c>
       <c r="N5" t="n">
         <v>-78969</v>
       </c>
+      <c r="O5" t="n">
+        <v>-5.31</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1413,26 +1361,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>1740</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>7069</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>-247</v>
       </c>
       <c r="H6" t="n">
-        <v>9146</v>
+        <v>8898</v>
       </c>
       <c r="I6" t="n">
         <v>-310</v>
       </c>
       <c r="J6" t="n">
-        <v>-120</v>
+        <v>-430</v>
       </c>
       <c r="K6" t="n">
         <v>149</v>
@@ -1441,11 +1389,14 @@
         <v>4858</v>
       </c>
       <c r="M6" t="n">
-        <v>20410</v>
+        <v>25268</v>
       </c>
       <c r="N6" t="n">
         <v>-649279</v>
       </c>
+      <c r="O6" t="n">
+        <v>15.81</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1468,26 +1419,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1990</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>31882</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-1275</v>
       </c>
       <c r="H7" t="n">
-        <v>33156</v>
+        <v>31880</v>
       </c>
       <c r="I7" t="n">
         <v>-4823</v>
       </c>
       <c r="J7" t="n">
-        <v>593</v>
+        <v>-4230</v>
       </c>
       <c r="K7" t="n">
         <v>432</v>
@@ -1496,11 +1447,14 @@
         <v>28141</v>
       </c>
       <c r="M7" t="n">
-        <v>106650</v>
+        <v>134791</v>
       </c>
       <c r="N7" t="n">
         <v>-6483078</v>
       </c>
+      <c r="O7" t="n">
+        <v>6.82</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1523,26 +1477,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1820</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-0.82</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>2933</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>64</v>
       </c>
       <c r="H8" t="n">
-        <v>-1323</v>
+        <v>-1258</v>
       </c>
       <c r="I8" t="n">
         <v>68</v>
       </c>
       <c r="J8" t="n">
-        <v>604</v>
+        <v>672</v>
       </c>
       <c r="K8" t="n">
         <v>52</v>
@@ -1551,11 +1505,14 @@
         <v>1632</v>
       </c>
       <c r="M8" t="n">
-        <v>7117</v>
+        <v>8749</v>
       </c>
       <c r="N8" t="n">
         <v>-140254</v>
       </c>
+      <c r="O8" t="n">
+        <v>12.89</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1578,26 +1535,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>1880</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>5.32</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>4603</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-1480</v>
       </c>
       <c r="H9" t="n">
-        <v>-703</v>
+        <v>-2183</v>
       </c>
       <c r="I9" t="n">
         <v>844</v>
       </c>
       <c r="J9" t="n">
-        <v>463</v>
+        <v>1307</v>
       </c>
       <c r="K9" t="n">
         <v>79</v>
@@ -1606,11 +1563,14 @@
         <v>1954</v>
       </c>
       <c r="M9" t="n">
-        <v>8082</v>
+        <v>10036</v>
       </c>
       <c r="N9" t="n">
         <v>-106297</v>
       </c>
+      <c r="O9" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1633,26 +1593,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>3325</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-2.78</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2472</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-331</v>
       </c>
       <c r="H10" t="n">
-        <v>504</v>
+        <v>173</v>
       </c>
       <c r="I10" t="n">
         <v>-125</v>
       </c>
       <c r="J10" t="n">
-        <v>305</v>
+        <v>180</v>
       </c>
       <c r="K10" t="n">
         <v>66</v>
@@ -1661,11 +1621,14 @@
         <v>1920</v>
       </c>
       <c r="M10" t="n">
-        <v>7513</v>
+        <v>9433</v>
       </c>
       <c r="N10" t="n">
         <v>-89543</v>
       </c>
+      <c r="O10" t="n">
+        <v>15.41</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1688,26 +1651,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2230</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-4.09</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>4703</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>-586</v>
       </c>
       <c r="H11" t="n">
-        <v>559</v>
+        <v>-27</v>
       </c>
       <c r="I11" t="n">
         <v>-40</v>
       </c>
       <c r="J11" t="n">
-        <v>-179</v>
+        <v>-219</v>
       </c>
       <c r="K11" t="n">
         <v>138</v>
@@ -1716,11 +1679,14 @@
         <v>4010</v>
       </c>
       <c r="M11" t="n">
-        <v>15408</v>
+        <v>19418</v>
       </c>
       <c r="N11" t="n">
         <v>-19421</v>
       </c>
+      <c r="O11" t="n">
+        <v>11.47</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1743,26 +1709,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>8560</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>7.94</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>525</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>-17</v>
       </c>
       <c r="H12" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
         <v>135</v>
       </c>
       <c r="J12" t="n">
-        <v>-66</v>
+        <v>69</v>
       </c>
       <c r="K12" t="n">
         <v>34</v>
@@ -1771,11 +1737,14 @@
         <v>289</v>
       </c>
       <c r="M12" t="n">
-        <v>1287</v>
+        <v>1576</v>
       </c>
       <c r="N12" t="n">
         <v>-9010</v>
       </c>
+      <c r="O12" t="n">
+        <v>14.04</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2320</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3045</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-221</v>
       </c>
       <c r="H13" t="n">
-        <v>-103</v>
+        <v>-324</v>
       </c>
       <c r="I13" t="n">
         <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>-173</v>
+        <v>-158</v>
       </c>
       <c r="K13" t="n">
         <v>26</v>
@@ -1826,11 +1795,14 @@
         <v>-92</v>
       </c>
       <c r="M13" t="n">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,26 +1825,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>465</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2933</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>195</v>
       </c>
       <c r="H14" t="n">
-        <v>-57</v>
+        <v>138</v>
       </c>
       <c r="I14" t="n">
         <v>-206</v>
       </c>
       <c r="J14" t="n">
-        <v>-430</v>
+        <v>-636</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1881,11 +1853,14 @@
         <v>-256</v>
       </c>
       <c r="M14" t="n">
-        <v>-539</v>
+        <v>-795</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,26 +1883,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1040</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2045</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>92</v>
       </c>
       <c r="H15" t="n">
-        <v>-236</v>
+        <v>-144</v>
       </c>
       <c r="I15" t="n">
         <v>-2</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>35</v>
@@ -1936,11 +1911,14 @@
         <v>-51</v>
       </c>
       <c r="M15" t="n">
-        <v>-126</v>
+        <v>-177</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1963,26 +1941,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1760</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" t="n">
-        <v>818</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="I16" t="n">
         <v>-2</v>
       </c>
       <c r="J16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K16" t="n">
         <v>7</v>
@@ -1991,11 +1969,14 @@
         <v>121</v>
       </c>
       <c r="M16" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2018,26 +1999,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="6" t="n">
         <v>614</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>-3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1466</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>-86</v>
       </c>
       <c r="H17" t="n">
-        <v>361</v>
+        <v>275</v>
       </c>
       <c r="I17" t="n">
         <v>-92</v>
       </c>
       <c r="J17" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>118</v>
@@ -2046,10 +2027,13 @@
         <v>9458</v>
       </c>
       <c r="M17" t="n">
-        <v>40452</v>
+        <v>49910</v>
       </c>
       <c r="N17" t="n">
         <v>-21582</v>
+      </c>
+      <c r="O17" t="n">
+        <v>47.39</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>

--- a/outputs/monitor_xlsx/20260413.xlsx
+++ b/outputs/monitor_xlsx/20260413.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1620</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9234</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>439</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-2640</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-525</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1721</v>
+      </c>
+      <c r="K18" t="n">
+        <v>196</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6674</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32457</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400965</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>626</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="F19" t="n">
+        <v>58280</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-30543</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-24072</v>
+      </c>
+      <c r="I19" t="n">
+        <v>31395</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34469</v>
+      </c>
+      <c r="K19" t="n">
+        <v>932</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35843</v>
+      </c>
+      <c r="M19" t="n">
+        <v>175541</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393452</v>
+      </c>
+      <c r="O19" t="n">
+        <v>15.87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>655</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9081</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-318</v>
+      </c>
+      <c r="H20" t="n">
+        <v>732</v>
+      </c>
+      <c r="I20" t="n">
+        <v>199</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4770</v>
+      </c>
+      <c r="K20" t="n">
+        <v>259</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8125</v>
+      </c>
+      <c r="M20" t="n">
+        <v>41690</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161018</v>
+      </c>
+      <c r="O20" t="n">
+        <v>14.06</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
